--- a/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,69 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>94000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>95872</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1,872</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>9.87%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>9.29%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3366000</v>
+        <v>11884000</v>
       </c>
       <c r="K2" t="n">
-        <v>2146000</v>
+        <v>11264000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-1,220,000</t>
+          <t>-620,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,55 +564,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>424000</v>
+        <v>11775450</v>
       </c>
       <c r="K3" t="n">
-        <v>448000</v>
+        <v>12668450</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>893,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,60 +622,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>90000</v>
+        <v>140000</v>
       </c>
       <c r="K4" t="n">
-        <v>130000</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>-139,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,60 +685,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>65000</v>
+        <v>341900</v>
       </c>
       <c r="K5" t="n">
-        <v>66294</v>
+        <v>313900</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1,294</t>
+          <t>-28,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -753,55 +753,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>157000</v>
+        <v>283000</v>
       </c>
       <c r="K6" t="n">
-        <v>137000</v>
+        <v>88000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-195,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>11.74%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59000</v>
+        <v>4200000</v>
       </c>
       <c r="K7" t="n">
-        <v>9000</v>
+        <v>4000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -874,114 +874,807 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>旺矽科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>旺矽科技</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>161000</v>
+        <v>460000</v>
       </c>
       <c r="K8" t="n">
-        <v>221000</v>
+        <v>380000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>-80,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6.62%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5.74%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>872000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>742000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-130,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08-27_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4.21%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.86%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.65%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4809000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5709000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>900,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-08-27_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5824000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6484000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>660,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08-27_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>632000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>382000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-250,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-08-27_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.59%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3366000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2146000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-1,220,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>424000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>448000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>24,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>+0.54%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>90000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>66294</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1,294</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>157000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>137000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.10%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>59000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>161000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>221000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>00993A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>5289</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>宜鼎國際</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>宜鼎國際</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>1.33%</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>1.36%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>+0.03%</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J20" t="n">
         <v>94000</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K20" t="n">
         <v>95872</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>1,872</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2026-08-27_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,60 +1126,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>632000</v>
+        <v>10378000</v>
       </c>
       <c r="K12" t="n">
-        <v>382000</v>
+        <v>11000000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-250,000</t>
+          <t>622,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-27_00992A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,60 +1189,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3366000</v>
+        <v>2500000</v>
       </c>
       <c r="K13" t="n">
-        <v>2146000</v>
+        <v>2800000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1,220,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,60 +1252,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>16.02%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>424000</v>
+        <v>12000000</v>
       </c>
       <c r="K14" t="n">
-        <v>448000</v>
+        <v>11100000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>-900,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1315,60 +1315,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>90000</v>
+        <v>15000000</v>
       </c>
       <c r="K15" t="n">
-        <v>130000</v>
+        <v>12000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>-3,000,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1383,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>65000</v>
+        <v>700000</v>
       </c>
       <c r="K16" t="n">
-        <v>66294</v>
+        <v>760000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1,294</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,60 +1441,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>157000</v>
+        <v>621000</v>
       </c>
       <c r="K17" t="n">
-        <v>137000</v>
+        <v>650000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,60 +1504,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>59000</v>
+        <v>1200000</v>
       </c>
       <c r="K18" t="n">
-        <v>9000</v>
+        <v>1293000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1567,60 +1567,60 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>161000</v>
+        <v>179500</v>
       </c>
       <c r="K19" t="n">
-        <v>221000</v>
+        <v>149500</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,48 +1635,237 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>94000</v>
+        <v>660000</v>
       </c>
       <c r="K20" t="n">
-        <v>95872</v>
+        <v>700000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1,872</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-27_00993A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>936000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>114,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>632000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>382000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-250,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-27_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1869,6 +1869,69 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>94000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>95872</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,872</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,60 +1126,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10378000</v>
+        <v>632000</v>
       </c>
       <c r="K12" t="n">
-        <v>11000000</v>
+        <v>382000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>622,000</t>
+          <t>-250,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,60 +1189,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2500000</v>
+        <v>3366000</v>
       </c>
       <c r="K13" t="n">
-        <v>2800000</v>
+        <v>2146000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>-1,220,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,60 +1252,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.19%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16.02%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12000000</v>
+        <v>424000</v>
       </c>
       <c r="K14" t="n">
-        <v>11100000</v>
+        <v>448000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-900,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1315,60 +1315,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15000000</v>
+        <v>90000</v>
       </c>
       <c r="K15" t="n">
-        <v>12000000</v>
+        <v>130000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-3,000,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1383,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>700000</v>
+        <v>65000</v>
       </c>
       <c r="K16" t="n">
-        <v>760000</v>
+        <v>66294</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>1,294</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,60 +1441,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>621000</v>
+        <v>157000</v>
       </c>
       <c r="K17" t="n">
-        <v>650000</v>
+        <v>137000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,60 +1504,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1200000</v>
+        <v>59000</v>
       </c>
       <c r="K18" t="n">
-        <v>1293000</v>
+        <v>9000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1567,60 +1567,60 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>179500</v>
+        <v>161000</v>
       </c>
       <c r="K19" t="n">
-        <v>149500</v>
+        <v>221000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,298 +1635,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>660000</v>
+        <v>94000</v>
       </c>
       <c r="K20" t="n">
-        <v>700000</v>
+        <v>95872</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>1,872</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>+0.23%</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>936000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>114,000</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>800000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>600000</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-200,000</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-08-27_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2.56%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1.58%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.98%</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>632000</v>
-      </c>
-      <c r="K23" t="n">
-        <v>382000</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-250,000</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-08-27_00992A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1.36%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>94000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>95872</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1,872</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
         <is>
           <t>2026-08-27_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-28_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,60 +1126,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>632000</v>
+        <v>10378000</v>
       </c>
       <c r="K12" t="n">
-        <v>382000</v>
+        <v>11000000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-250,000</t>
+          <t>622,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-27_00992A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,60 +1189,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3366000</v>
+        <v>2500000</v>
       </c>
       <c r="K13" t="n">
-        <v>2146000</v>
+        <v>2800000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1,220,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,60 +1252,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>16.02%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>424000</v>
+        <v>12000000</v>
       </c>
       <c r="K14" t="n">
-        <v>448000</v>
+        <v>11100000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>-900,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1315,60 +1315,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>90000</v>
+        <v>15000000</v>
       </c>
       <c r="K15" t="n">
-        <v>130000</v>
+        <v>12000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>-3,000,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1383,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>65000</v>
+        <v>700000</v>
       </c>
       <c r="K16" t="n">
-        <v>66294</v>
+        <v>760000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1,294</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,60 +1441,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>157000</v>
+        <v>621000</v>
       </c>
       <c r="K17" t="n">
-        <v>137000</v>
+        <v>650000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,60 +1504,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>59000</v>
+        <v>1200000</v>
       </c>
       <c r="K18" t="n">
-        <v>9000</v>
+        <v>1293000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1567,114 +1567,807 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>161000</v>
+        <v>179500</v>
       </c>
       <c r="K19" t="n">
-        <v>221000</v>
+        <v>149500</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.67%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.01%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>660000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>700000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>936000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>114,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08-27_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>632000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>382000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-250,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-27_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.59%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3366000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2146000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-1,220,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>424000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>448000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>24,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.54%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>90000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>66294</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,294</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>157000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>137000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-1.10%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>59000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>161000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>221000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-08-27_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>00993A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>5289</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>宜鼎國際</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>宜鼎國際</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>1.33%</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>1.36%</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>+0.03%</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J31" t="n">
         <v>94000</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K31" t="n">
         <v>95872</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>1,872</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2026-08-27_00993A_full_holdings.xlsx</t>
         </is>
